--- a/artfynd/A 57833-2023 artfynd.xlsx
+++ b/artfynd/A 57833-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132439741</v>
+        <v>132439737</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551384</v>
+        <v>551365</v>
       </c>
       <c r="R2" t="n">
-        <v>6709617</v>
+        <v>6709661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132439719</v>
+        <v>132439692</v>
       </c>
       <c r="B3" t="n">
-        <v>93244</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551499</v>
+        <v>551403</v>
       </c>
       <c r="R3" t="n">
-        <v>6709773</v>
+        <v>6709817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,50 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132439732</v>
+        <v>132439738</v>
       </c>
       <c r="B4" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551376</v>
+        <v>551356</v>
       </c>
       <c r="R4" t="n">
-        <v>6709664</v>
+        <v>6709642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,42 +1005,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132439740</v>
+        <v>132439744</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551391</v>
+        <v>551410</v>
       </c>
       <c r="R5" t="n">
-        <v>6709619</v>
+        <v>6709633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132439744</v>
+        <v>132439731</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,27 +1128,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1166,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551410</v>
+        <v>551403</v>
       </c>
       <c r="R6" t="n">
-        <v>6709633</v>
+        <v>6709686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132439750</v>
+        <v>132439732</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551490</v>
+        <v>551376</v>
       </c>
       <c r="R7" t="n">
-        <v>6709667</v>
+        <v>6709664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132439747</v>
+        <v>132439736</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1372,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1390,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551451</v>
+        <v>551353</v>
       </c>
       <c r="R8" t="n">
-        <v>6709647</v>
+        <v>6709650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,42 +1453,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132439739</v>
+        <v>132439745</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>8460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1506,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551352</v>
+        <v>551409</v>
       </c>
       <c r="R9" t="n">
-        <v>6709640</v>
+        <v>6709629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,38 +1565,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132439723</v>
+        <v>132439739</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1618,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551418</v>
+        <v>551352</v>
       </c>
       <c r="R10" t="n">
-        <v>6709740</v>
+        <v>6709640</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,42 +1681,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132439737</v>
+        <v>132439740</v>
       </c>
       <c r="B11" t="n">
-        <v>93206</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1734,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551365</v>
+        <v>551391</v>
       </c>
       <c r="R11" t="n">
-        <v>6709661</v>
+        <v>6709619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,42 +1797,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132439728</v>
+        <v>132439741</v>
       </c>
       <c r="B12" t="n">
-        <v>93206</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1850,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551422</v>
+        <v>551384</v>
       </c>
       <c r="R12" t="n">
-        <v>6709703</v>
+        <v>6709617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,38 +1913,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132439731</v>
+        <v>132439742</v>
       </c>
       <c r="B13" t="n">
-        <v>58119</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551403</v>
+        <v>551385</v>
       </c>
       <c r="R13" t="n">
-        <v>6709686</v>
+        <v>6709617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,32 +2029,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132439720</v>
+        <v>132439721</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>92188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551445</v>
+        <v>551451</v>
       </c>
       <c r="R14" t="n">
-        <v>6709769</v>
+        <v>6709768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,32 +2136,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132439718</v>
+        <v>132439730</v>
       </c>
       <c r="B15" t="n">
-        <v>93244</v>
+        <v>92188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>3008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551494</v>
+        <v>551419</v>
       </c>
       <c r="R15" t="n">
-        <v>6709778</v>
+        <v>6709682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,38 +2243,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132439745</v>
+        <v>132439725</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>93271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2288,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551409</v>
+        <v>551425</v>
       </c>
       <c r="R16" t="n">
-        <v>6709629</v>
+        <v>6709735</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,38 +2359,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132439736</v>
+        <v>132439726</v>
       </c>
       <c r="B17" t="n">
-        <v>8455</v>
+        <v>93271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2400,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551353</v>
+        <v>551431</v>
       </c>
       <c r="R17" t="n">
-        <v>6709650</v>
+        <v>6709716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,42 +2475,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132439742</v>
+        <v>132439728</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>93271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2516,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551385</v>
+        <v>551422</v>
       </c>
       <c r="R18" t="n">
-        <v>6709617</v>
+        <v>6709703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132439738</v>
+        <v>132439718</v>
       </c>
       <c r="B19" t="n">
-        <v>79952</v>
+        <v>93309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,21 +2602,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551356</v>
+        <v>551494</v>
       </c>
       <c r="R19" t="n">
-        <v>6709642</v>
+        <v>6709778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132439727</v>
+        <v>132439719</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>93309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2730,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551425</v>
+        <v>551499</v>
       </c>
       <c r="R20" t="n">
-        <v>6709701</v>
+        <v>6709773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132439722</v>
+        <v>132439720</v>
       </c>
       <c r="B21" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551422</v>
+        <v>551445</v>
       </c>
       <c r="R21" t="n">
-        <v>6709732</v>
+        <v>6709769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2875,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2885,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,54 +2912,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132439725</v>
+        <v>132439722</v>
       </c>
       <c r="B22" t="n">
-        <v>93206</v>
+        <v>79992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551425</v>
+        <v>551422</v>
       </c>
       <c r="R22" t="n">
-        <v>6709735</v>
+        <v>6709732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3025,54 +3019,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132439726</v>
+        <v>132439727</v>
       </c>
       <c r="B23" t="n">
-        <v>93206</v>
+        <v>79992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551431</v>
+        <v>551425</v>
       </c>
       <c r="R23" t="n">
-        <v>6709716</v>
+        <v>6709701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3104,7 +3089,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3114,7 +3099,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,50 +3126,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132439724</v>
+        <v>132439743</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>551424</v>
+        <v>551418</v>
       </c>
       <c r="R24" t="n">
-        <v>6709735</v>
+        <v>6709609</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3216,7 +3196,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3226,7 +3206,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,50 +3233,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132439751</v>
+        <v>132439759</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>551515</v>
+        <v>551568</v>
       </c>
       <c r="R25" t="n">
-        <v>6709653</v>
+        <v>6709559</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3328,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3338,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3365,35 +3340,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132439743</v>
+        <v>132439723</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
@@ -3403,7 +3383,7 @@
         <v>551418</v>
       </c>
       <c r="R26" t="n">
-        <v>6709609</v>
+        <v>6709740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3435,7 +3415,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3445,7 +3425,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,6 +3449,780 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132439724</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>551424</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6709735</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132439747</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>551451</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6709647</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132439750</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>551490</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6709667</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132439751</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>551515</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6709653</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132439757</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>551607</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6709616</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132439693</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>551430</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6709832</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132439758</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>551595</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6709572</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57833-2023 artfynd.xlsx
+++ b/artfynd/A 57833-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439721</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439726</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439737</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439718</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439719</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439692</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439720</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439722</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439727</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439738</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439743</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,6 +2388,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439759</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2425,6 +2505,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439723</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439744</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2649,6 +2739,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439731</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2761,6 +2856,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439724</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2873,6 +2973,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439732</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2985,6 +3090,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439736</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3097,6 +3207,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439745</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3209,6 +3324,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439747</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3321,6 +3441,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439750</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3433,6 +3558,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439751</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3545,6 +3675,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439757</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3661,6 +3796,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439739</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439740</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3893,6 +4038,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439741</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4009,6 +4159,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439742</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4116,6 +4271,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439693</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4223,8 +4383,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>